--- a/data/raw_data/nashik_raw_data.xlsx
+++ b/data/raw_data/nashik_raw_data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Farheen\DSE-Compass\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5F9FB6-29E7-448D-BD98-E61306C1F768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C71797-B8A6-406F-B988-6CB12E7FB3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="college_details" sheetId="1" r:id="rId1"/>
-    <sheet name="branches" sheetId="2" r:id="rId2"/>
-    <sheet name="cutoffs" sheetId="3" r:id="rId3"/>
-    <sheet name="placement_stats" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="branches" sheetId="2" r:id="rId3"/>
+    <sheet name="cutoffs" sheetId="3" r:id="rId4"/>
+    <sheet name="placement_stats" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="91">
   <si>
     <t>college_id</t>
   </si>
@@ -151,13 +152,193 @@
   </si>
   <si>
     <t>avg_package</t>
+  </si>
+  <si>
+    <t>college list</t>
+  </si>
+  <si>
+    <t>abhinav institue of technology and management - nashik campus</t>
+  </si>
+  <si>
+    <t>brahma valley college of engineering and research institute</t>
+  </si>
+  <si>
+    <t>eminent institute of management and technology</t>
+  </si>
+  <si>
+    <t>indian railways institute of electrical engineering</t>
+  </si>
+  <si>
+    <t>jawahar education society's institute of technology, management and research</t>
+  </si>
+  <si>
+    <t>kk wagh institute of engineering education and research</t>
+  </si>
+  <si>
+    <t>kvn naik college of engineering and research institute</t>
+  </si>
+  <si>
+    <t>late gn sapkal college of engineering</t>
+  </si>
+  <si>
+    <t>late sau. Kantabai bhavarlalji jain college of engineering</t>
+  </si>
+  <si>
+    <t>matoshri college of engineering and research center</t>
+  </si>
+  <si>
+    <t>met institute of engineering</t>
+  </si>
+  <si>
+    <t>nashik district maratha vidya prasarak samaj's kbt college of engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rh sapat college of engineering, </t>
+  </si>
+  <si>
+    <t>sahyadri college of fire engineering and safety management</t>
+  </si>
+  <si>
+    <t>sandip institute of engineering and management - siem</t>
+  </si>
+  <si>
+    <t>sandip institute of technology and research center - sitrc</t>
+  </si>
+  <si>
+    <t>sandip university</t>
+  </si>
+  <si>
+    <t>sanghavi college of engineering</t>
+  </si>
+  <si>
+    <t>shatabdi institute ofengineering and research</t>
+  </si>
+  <si>
+    <t>sir visvesvaraya memorial engineering college</t>
+  </si>
+  <si>
+    <t>snd college of engineering and research center - sndcoerc</t>
+  </si>
+  <si>
+    <t>yashwantrao chavan maharashtra open university</t>
+  </si>
+  <si>
+    <t>pune vidyarthi griha's college of engineering</t>
+  </si>
+  <si>
+    <t>Nashik</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>aicte_approved</t>
+  </si>
+  <si>
+    <t>study center affialated to ycmou rather than a college</t>
+  </si>
+  <si>
+    <t>Brahma Valley College of Engineering and Research Institute</t>
+  </si>
+  <si>
+    <t>https://engineering.brahmavalley.edu.in/</t>
+  </si>
+  <si>
+    <t>Computer Engineering</t>
+  </si>
+  <si>
+    <t>Civil Engineering</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>Electrical Engineering</t>
+  </si>
+  <si>
+    <t>BVCERI</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>3.31 L</t>
+  </si>
+  <si>
+    <t>Anjaneri, Trimbak Road,Nashik, Maharashtra — 422213, India</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <r>
+      <t>+91 7743895341</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+91 8087561281</t>
+    </r>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>CIVIL</t>
+  </si>
+  <si>
+    <t>ELEC</t>
+  </si>
+  <si>
+    <t>MECH</t>
+  </si>
+  <si>
+    <t>no dte code, based in aurangabad</t>
+  </si>
+  <si>
+    <t>no dte code, only for officers in indian railways - no civilians</t>
+  </si>
+  <si>
+    <t>Jawahar Education Society's Institute of Technology, Management and Research</t>
+  </si>
+  <si>
+    <t>B++</t>
+  </si>
+  <si>
+    <t>0253-2970077</t>
+  </si>
+  <si>
+    <t>https://jitnashik.edu.in/jit-main/</t>
+  </si>
+  <si>
+    <t>JIT</t>
+  </si>
+  <si>
+    <t>not found</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,6 +362,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -199,17 +401,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -488,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -497,16 +703,17 @@
     <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -538,28 +745,31 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -591,25 +801,252 @@
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>5130</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q3" r:id="rId1" xr:uid="{F6E512A5-F9E2-4046-B4C3-5669B0DEE808}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C10441-00F6-428B-8BE2-0782171B2BC2}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -617,9 +1054,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFA7DCD-D4FF-479A-B6E2-9169105A0CFA}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -669,61 +1106,84 @@
         <v>24</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4330971E-46F0-4063-9D60-3EA0B29B5B12}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>5130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4">
+        <v>5130</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>33</v>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>5130</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6">
+        <v>5130</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -732,8 +1192,72 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4330971E-46F0-4063-9D60-3EA0B29B5B12}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9C70A4-AF5C-4FEB-AEFC-E875D37DF429}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -784,6 +1308,66 @@
         <v>23</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>5130</v>
+      </c>
+      <c r="D3">
+        <v>2025</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4">
+        <v>5130</v>
+      </c>
+      <c r="D4">
+        <v>2024</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>5130</v>
+      </c>
+      <c r="D5">
+        <v>2023</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/raw_data/nashik_raw_data.xlsx
+++ b/data/raw_data/nashik_raw_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Farheen\DSE-Compass\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C71797-B8A6-406F-B988-6CB12E7FB3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53396593-1643-483D-9C08-B8083E0A4D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="college_details" sheetId="1" r:id="rId1"/>
@@ -338,7 +338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,13 +383,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -405,14 +418,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -694,216 +731,209 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="18" width="15.77734375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="12">
         <v>5130</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="7">
         <v>2008</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="7" t="s">
         <v>88</v>
       </c>
     </row>
@@ -926,7 +956,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H2" t="s">
@@ -939,7 +969,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="H4" t="s">
@@ -947,7 +977,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H5" t="s">
@@ -1051,6 +1081,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1059,130 +1090,131 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="12"/>
+    <col min="4" max="4" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="12">
         <v>5130</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="12">
         <v>5130</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="12">
         <v>5130</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="12">
         <v>5130</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="12">
         <v>120</v>
       </c>
     </row>

--- a/data/raw_data/nashik_raw_data.xlsx
+++ b/data/raw_data/nashik_raw_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Farheen\DSE-Compass\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53396593-1643-483D-9C08-B8083E0A4D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F010815F-5D34-47AE-8B53-CABEC2060CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="college_details" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="197">
   <si>
     <t>college_id</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>naac_grade</t>
-  </si>
-  <si>
-    <t>ugc_approved</t>
   </si>
   <si>
     <t>contact_no</t>
@@ -123,9 +120,6 @@
     <t>branch_abbrv</t>
   </si>
   <si>
-    <t>intake_capacity</t>
-  </si>
-  <si>
     <t>cutoff_id</t>
   </si>
   <si>
@@ -173,9 +167,6 @@
   </si>
   <si>
     <t>kk wagh institute of engineering education and research</t>
-  </si>
-  <si>
-    <t>kvn naik college of engineering and research institute</t>
   </si>
   <si>
     <t>late gn sapkal college of engineering</t>
@@ -331,14 +322,341 @@
     <t>JIT</t>
   </si>
   <si>
-    <t>not found</t>
+    <t>regular_intake</t>
+  </si>
+  <si>
+    <t>latest_dse_intake</t>
+  </si>
+  <si>
+    <t>Survey No 48, Gowardhan, Gangapur Road, Nashik, Maharashtra 422222, India.</t>
+  </si>
+  <si>
+    <t>1.73 L - 2.31 L</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence &amp; Data Science</t>
+  </si>
+  <si>
+    <t>Electronic &amp; Computer Engineering</t>
+  </si>
+  <si>
+    <t>Automation &amp; Robotics</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>AIDS</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>K. K. Wagh Institute of Engineering Education &amp; Research</t>
+  </si>
+  <si>
+    <t>KKWEIR</t>
+  </si>
+  <si>
+    <t>Hirabai Haridas Vidyanagari, Mumbai Agra Road Amrutdham, Panchavati, Nashik, Maharashtra 422003</t>
+  </si>
+  <si>
+    <t>0253 251 2876</t>
+  </si>
+  <si>
+    <t>3.68 L - 5.67 L</t>
+  </si>
+  <si>
+    <t>Electronic &amp; Telecommunication Engineering</t>
+  </si>
+  <si>
+    <t>Chemical Engineering</t>
+  </si>
+  <si>
+    <t>Robotics &amp; Automation Engineering</t>
+  </si>
+  <si>
+    <t>Computer Science and Design</t>
+  </si>
+  <si>
+    <t>CHEM</t>
+  </si>
+  <si>
+    <t>https://www.kkwagh.edu.in/engineering</t>
+  </si>
+  <si>
+    <t>R&amp;A</t>
+  </si>
+  <si>
+    <t>CSD</t>
+  </si>
+  <si>
+    <t>E&amp;C</t>
+  </si>
+  <si>
+    <t>E&amp;TC</t>
+  </si>
+  <si>
+    <t>Dongare Vasatigruha Parisar, Vasantrao Naik Chowk, Canada Corner, Nashik - 422002.</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>LOGMIEER</t>
+  </si>
+  <si>
+    <t>Loknete Gopinathji Munde Institute of Engineering Education &amp; Research (a.k.a K.V.N. Naik Institute of Engineering Education &amp; Research)</t>
+  </si>
+  <si>
+    <t>https://www.logmieer.edu.in/</t>
+  </si>
+  <si>
+    <t>3.2 L</t>
+  </si>
+  <si>
+    <t>0253 6641300</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence &amp; Machine Learning</t>
+  </si>
+  <si>
+    <t>AIML</t>
+  </si>
+  <si>
+    <t>2.1 L - 3.5 L</t>
+  </si>
+  <si>
+    <t>25 - 50 %</t>
+  </si>
+  <si>
+    <t>50 - 60%</t>
+  </si>
+  <si>
+    <t>2.0 L - 4.5 L</t>
+  </si>
+  <si>
+    <t>80 - 90.43%</t>
+  </si>
+  <si>
+    <t>4.8 L - 5.5 L</t>
+  </si>
+  <si>
+    <t>40 - 50%</t>
+  </si>
+  <si>
+    <t>2.2 L - 3.6 L</t>
+  </si>
+  <si>
+    <t>kvn naik college of engineering and research institute (logmieer)</t>
+  </si>
+  <si>
+    <t>Late G.N. Sapkal College of Engineering</t>
+  </si>
+  <si>
+    <t>LGNSCOE</t>
+  </si>
+  <si>
+    <t>Kalyani Hills, Anjaneri-Wadholi, Trimbakeshwar Road, Nashik - 422213, Maharashtra.</t>
+  </si>
+  <si>
+    <t>45 - 50 %</t>
+  </si>
+  <si>
+    <t>3.5 L - 5 L</t>
+  </si>
+  <si>
+    <t>5182 / 6115</t>
+  </si>
+  <si>
+    <t>https://www.lgnscoe.sapkalknowledgehub.org/</t>
+  </si>
+  <si>
+    <t>1800 233 2999 / 094206 95484</t>
+  </si>
+  <si>
+    <t>1.99 L - 3.06 L</t>
+  </si>
+  <si>
+    <t>LGNSCCOE</t>
+  </si>
+  <si>
+    <t>5183 / 6115</t>
+  </si>
+  <si>
+    <t>5184 / 6115</t>
+  </si>
+  <si>
+    <t>5185 / 6115</t>
+  </si>
+  <si>
+    <t>5186 / 6115</t>
+  </si>
+  <si>
+    <t>5187 / 6115</t>
+  </si>
+  <si>
+    <t>SNJB's Late Sau. Kantabai Bhavarlalji Jain College of Engineering</t>
+  </si>
+  <si>
+    <t>SNJB</t>
+  </si>
+  <si>
+    <t>Chandwad</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Neminagar, Chandwad, Nashik, Maharashtra - 423101</t>
+  </si>
+  <si>
+    <t>3.93 L</t>
+  </si>
+  <si>
+    <t>3.5 L</t>
+  </si>
+  <si>
+    <t>4.97 L</t>
+  </si>
+  <si>
+    <t>https://www.snjb.org/engineering/</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Telecommunication</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Telecommunication Engineering</t>
+  </si>
+  <si>
+    <t>Matoshri College of Engineering &amp; Research Centre</t>
+  </si>
+  <si>
+    <t>MCOERC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Eklahareshivar, Near Odha Village, Opp. Nashik-Chhatrapati Sambhaji Nagar (Aurangabad) Highway, Nashik, Maharashtra 422105, India.</t>
+  </si>
+  <si>
+    <t>253 240 6600</t>
+  </si>
+  <si>
+    <t>https://engg.matoshri.edu.in/</t>
+  </si>
+  <si>
+    <t>Eklahare</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Computer Engineering</t>
+  </si>
+  <si>
+    <t>2.88 L - 3.2 L</t>
+  </si>
+  <si>
+    <t>3 L</t>
+  </si>
+  <si>
+    <t>4.5 L</t>
+  </si>
+  <si>
+    <t>MET Institute of Engineering, Bhujbal Knowledge City</t>
+  </si>
+  <si>
+    <t>98811 00099</t>
+  </si>
+  <si>
+    <t>Unnamed Road, 422207, Bhujbal Knowledge City, Adgaon, Nashik, Maharashtra 422003</t>
+  </si>
+  <si>
+    <t>Adgaon</t>
+  </si>
+  <si>
+    <t>METIOE</t>
+  </si>
+  <si>
+    <t>https://metbkcengg.ac.in/</t>
+  </si>
+  <si>
+    <t>4.23 L</t>
+  </si>
+  <si>
+    <t>ugc_recognized</t>
+  </si>
+  <si>
+    <t>yes (section - 2(f), 12(B))</t>
+  </si>
+  <si>
+    <t>MVP Karmaveer Adv. Baburao Ganpatrao Thakare College of Engineering</t>
+  </si>
+  <si>
+    <t>KBTCOE</t>
+  </si>
+  <si>
+    <t>Udoji Maratha Boarding Campus, Gangapur Rd, Nashik, Maharashtra 422013</t>
+  </si>
+  <si>
+    <t>86982 64455</t>
+  </si>
+  <si>
+    <t>2.76 L - 4.1 L</t>
+  </si>
+  <si>
+    <t>https://kbtcoe.org/</t>
+  </si>
+  <si>
+    <t>Instrumentation &amp; Control Engineering</t>
+  </si>
+  <si>
+    <t>4 L</t>
+  </si>
+  <si>
+    <t>A++</t>
+  </si>
+  <si>
+    <t>KBT</t>
+  </si>
+  <si>
+    <t>Pune Vidyarthi Griha's College of Engineering &amp; S. S. Dhamankar Institute of Management, Nashik</t>
+  </si>
+  <si>
+    <t>Mhasrul Gaon</t>
+  </si>
+  <si>
+    <t>0253 648 0000</t>
+  </si>
+  <si>
+    <t>https://www.pvgcoenashik.org/</t>
+  </si>
+  <si>
+    <t>PVGCOE</t>
+  </si>
+  <si>
+    <t>206, Dindori Rd, behind Reliance Petrol Pump, Gorksha Nagar, Near MERI, Mhasrul Gaon, Nashik, Maharashtra 422004</t>
+  </si>
+  <si>
+    <t>2.58 L</t>
+  </si>
+  <si>
+    <t>65 - 70%</t>
+  </si>
+  <si>
+    <t>4.20 L - 5 L</t>
+  </si>
+  <si>
+    <t>3.80 L - 4.50 L</t>
+  </si>
+  <si>
+    <t>3.50 L - 4.12 L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +708,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -405,7 +729,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -413,18 +737,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -450,6 +853,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -731,215 +1180,702 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="18" width="15.77734375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="18" width="15.77734375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <v>5130</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="R3" s="6">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11">
+        <v>5401</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="R4" s="6">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11">
+        <v>5121</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="R5" s="6">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11">
+        <v>5390</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="R6" s="6">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="R7" s="6">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11">
+        <v>5173</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M8" s="6">
+        <v>2556253750</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="R8" s="6">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11">
+        <v>5177</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="R9" s="6">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11">
+        <v>5151</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="R10" s="6">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11">
+        <v>5108</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="R11" s="6">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
-        <v>1</v>
-      </c>
-      <c r="B3" s="12">
-        <v>5130</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="B12" s="11">
+        <v>5330</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="R3" s="7">
-        <v>2008</v>
-      </c>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>88</v>
+      <c r="K12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="R12" s="6">
+        <v>2010</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="Q3" r:id="rId1" xr:uid="{F6E512A5-F9E2-4046-B4C3-5669B0DEE808}"/>
+    <hyperlink ref="Q5" r:id="rId2" xr:uid="{0B6C0AF0-5D3F-4832-840F-5488BCA44B6B}"/>
+    <hyperlink ref="Q4" r:id="rId3" xr:uid="{17C90922-4F15-4D49-B9ED-880F1E353D69}"/>
+    <hyperlink ref="Q6" r:id="rId4" xr:uid="{42100117-AB83-428B-A302-F1C57C11EB2E}"/>
+    <hyperlink ref="Q7" r:id="rId5" xr:uid="{149D5733-5816-468B-87D8-EB61A262AD54}"/>
+    <hyperlink ref="Q8" r:id="rId6" xr:uid="{5EF54DA0-9733-4F5D-A0FB-B54DED2F5903}"/>
+    <hyperlink ref="Q9" r:id="rId7" xr:uid="{4DC4D018-AB2C-4C55-9695-DF499D9CB60E}"/>
+    <hyperlink ref="Q10" r:id="rId8" xr:uid="{FFB3ECAC-D848-4E15-970D-68B028BECAD0}"/>
+    <hyperlink ref="Q11" r:id="rId9" xr:uid="{D947DA4C-7292-44A1-BD7F-81848DC873C7}"/>
+    <hyperlink ref="M12" r:id="rId10" display="https://www.google.com/search?q=pune+vidyarthi+griha%27s+college+of+engineering+nashik&amp;sca_esv=8712aa7b0522de6e&amp;rlz=1C1RXQR_enIN1094IN1094&amp;sxsrf=APpeQntmnHnluQT8yVmJNDjaeRoh0FECRg%3A1781875280314&amp;ei=UEI1atHcEtiUseMPiuvboAE&amp;biw=767&amp;bih=730&amp;ved=0ahUKEwjRxPfYspOVAxVYSmwGHYr1FhQQ4dUDCBI&amp;uact=5&amp;oq=pune+vidyarthi+griha%27s+college+of+engineering+nashik&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiNHB1bmUgdmlkeWFydGhpIGdyaWhhJ3MgY29sbGVnZSBvZiBlbmdpbmVlcmluZyBuYXNoaWtIAFAAWABwAHgBkAEAmAEAoAEAqgEAuAEDyAEA-AEBmAIAoAIAmAMAkgcAoAcAsgcAuAcAwgcAyAcAgAgB&amp;sclient=gws-wiz-serp" xr:uid="{781D89A6-6713-4250-95E3-16EC255163F0}"/>
+    <hyperlink ref="Q12" r:id="rId11" xr:uid="{34647692-C414-4AF3-A409-B1F9853569FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -952,131 +1888,131 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="H4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="H5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1087,145 +2023,1398 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFA7DCD-D4FF-479A-B6E2-9169105A0CFA}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="12"/>
-    <col min="4" max="4" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="11"/>
+    <col min="4" max="4" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="E1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="15">
+        <v>5130</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="15">
+        <v>60</v>
+      </c>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="11">
+        <v>5130</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="11">
+        <v>60</v>
+      </c>
+      <c r="G4" s="19"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
         <v>3</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="B5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="11">
+        <v>5130</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="11">
+        <v>60</v>
+      </c>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="20">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="21">
+        <v>5130</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="21">
+        <v>120</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="15">
+        <v>5401</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="15">
+        <v>120</v>
+      </c>
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="11">
+        <v>5401</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="11">
+        <v>120</v>
+      </c>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="11">
+        <v>5401</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="11">
+        <v>120</v>
+      </c>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="11">
+        <v>5401</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="11">
+        <v>60</v>
+      </c>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="18">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="11">
+        <v>5401</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="11">
+        <v>23</v>
+      </c>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>10</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="11">
+        <v>5401</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="11">
+        <v>46</v>
+      </c>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <v>11</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="11">
+        <v>5401</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="11">
+        <v>60</v>
+      </c>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="20">
+        <v>12</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="21">
+        <v>5401</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="21">
+        <v>60</v>
+      </c>
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>13</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="15">
+        <v>5121</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="15">
+        <v>120</v>
+      </c>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
+        <v>14</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="11">
+        <v>120</v>
+      </c>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>15</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="11">
+        <v>120</v>
+      </c>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="11">
+        <v>120</v>
+      </c>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <v>17</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="11">
+        <v>120</v>
+      </c>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <v>18</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="11">
+        <v>60</v>
+      </c>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="18">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="11">
+        <v>120</v>
+      </c>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="18">
+        <v>20</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="11">
+        <v>120</v>
+      </c>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="18">
+        <v>21</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="11">
+        <v>5121</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="11">
+        <v>120</v>
+      </c>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="20">
+        <v>22</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="21">
+        <v>5121</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="21">
+        <v>120</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="14">
+        <v>23</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="15">
+        <v>5390</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="15">
+        <v>60</v>
+      </c>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
+        <v>24</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="11">
+        <v>5390</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="11">
+        <v>60</v>
+      </c>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="18">
+        <v>25</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="11">
+        <v>5390</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="11">
+        <v>30</v>
+      </c>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
         <v>26</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="B28" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="11">
+        <v>5390</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="11">
+        <v>60</v>
+      </c>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
         <v>27</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="B29" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="11">
+        <v>5390</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="11">
+        <v>60</v>
+      </c>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="20">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
-        <v>1</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="B30" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="21">
+        <v>5390</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="21">
+        <v>60</v>
+      </c>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
+        <v>29</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="15">
+        <v>120</v>
+      </c>
+      <c r="G31" s="17"/>
+    </row>
+    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
+        <v>30</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="11">
+        <v>120</v>
+      </c>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="18">
+        <v>31</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="11">
+        <v>60</v>
+      </c>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
+        <v>32</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="11">
+        <v>60</v>
+      </c>
+      <c r="G34" s="19"/>
+    </row>
+    <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="18">
+        <v>33</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="11">
+        <v>120</v>
+      </c>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="20">
+        <v>34</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="21">
+        <v>60</v>
+      </c>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="14">
+        <v>35</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="15">
+        <v>5173</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" s="15">
+        <v>126</v>
+      </c>
+      <c r="G37" s="17"/>
+    </row>
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="18">
+        <v>36</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="11">
+        <v>63</v>
+      </c>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="18">
+        <v>37</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="11">
+        <v>189</v>
+      </c>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="18">
+        <v>38</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="11">
+        <v>63</v>
+      </c>
+      <c r="G40" s="19"/>
+    </row>
+    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="20">
+        <v>39</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="21">
+        <v>63</v>
+      </c>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="14">
+        <v>40</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" s="15"/>
+      <c r="D42" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="15">
+        <v>120</v>
+      </c>
+      <c r="G42" s="17"/>
+    </row>
+    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="18">
+        <v>41</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="11">
+        <v>60</v>
+      </c>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="18">
+        <v>42</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="11">
+        <v>180</v>
+      </c>
+      <c r="G44" s="19"/>
+    </row>
+    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="18">
+        <v>43</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="11">
+        <v>60</v>
+      </c>
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="18">
+        <v>44</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" s="11">
+        <v>120</v>
+      </c>
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="18">
+        <v>45</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F47" s="11">
+        <v>120</v>
+      </c>
+      <c r="G47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="18">
+        <v>46</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F48" s="11">
+        <v>120</v>
+      </c>
+      <c r="G48" s="19"/>
+    </row>
+    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="20">
+        <v>47</v>
+      </c>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49" s="21">
+        <v>120</v>
+      </c>
+      <c r="G49" s="23"/>
+    </row>
+    <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="14">
+        <v>48</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" s="15">
+        <v>120</v>
+      </c>
+      <c r="G50" s="17"/>
+    </row>
+    <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="18">
+        <v>49</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="11">
+        <v>120</v>
+      </c>
+      <c r="G51" s="19"/>
+    </row>
+    <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="18">
+        <v>50</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F52" s="11">
+        <v>120</v>
+      </c>
+      <c r="G52" s="19"/>
+    </row>
+    <row r="53" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="18">
+        <v>51</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F53" s="11">
+        <v>60</v>
+      </c>
+      <c r="G53" s="19"/>
+    </row>
+    <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="18">
+        <v>52</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" s="11">
+        <v>120</v>
+      </c>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="18">
+        <v>53</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="11">
+        <v>60</v>
+      </c>
+      <c r="G55" s="19"/>
+    </row>
+    <row r="56" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="18">
+        <v>54</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56" s="11">
+        <v>60</v>
+      </c>
+      <c r="G56" s="19"/>
+    </row>
+    <row r="57" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="20">
+        <v>55</v>
+      </c>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F57" s="21">
+        <v>60</v>
+      </c>
+      <c r="G57" s="23"/>
+    </row>
+    <row r="58" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="14">
+        <v>56</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="15"/>
+      <c r="D58" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15">
+        <v>120</v>
+      </c>
+      <c r="G58" s="17"/>
+    </row>
+    <row r="59" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="18">
+        <v>57</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F59" s="11">
+        <v>180</v>
+      </c>
+      <c r="G59" s="19"/>
+    </row>
+    <row r="60" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="18">
+        <v>58</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" s="11">
+        <v>60</v>
+      </c>
+      <c r="G60" s="19"/>
+    </row>
+    <row r="61" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="18">
+        <v>59</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F61" s="11">
+        <v>120</v>
+      </c>
+      <c r="G61" s="19"/>
+    </row>
+    <row r="62" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="18">
+        <v>60</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F62" s="11">
+        <v>120</v>
+      </c>
+      <c r="G62" s="19"/>
+    </row>
+    <row r="63" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="18">
+        <v>61</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F63" s="11">
+        <v>180</v>
+      </c>
+      <c r="G63" s="19"/>
+    </row>
+    <row r="64" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="18">
+        <v>62</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F64" s="11">
+        <v>180</v>
+      </c>
+      <c r="G64" s="19"/>
+    </row>
+    <row r="65" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="18">
+        <v>63</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F65" s="11">
+        <v>60</v>
+      </c>
+      <c r="G65" s="19"/>
+    </row>
+    <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="20">
+        <v>64</v>
+      </c>
+      <c r="B66" s="21"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21">
+        <v>120</v>
+      </c>
+      <c r="G66" s="23"/>
+    </row>
+    <row r="67" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="14">
+        <v>65</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="15"/>
+      <c r="D67" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" s="15"/>
+      <c r="G67" s="17"/>
+    </row>
+    <row r="68" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="18">
+        <v>66</v>
+      </c>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="F68" s="31"/>
+      <c r="G68" s="19"/>
+    </row>
+    <row r="69" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="18">
+        <v>67</v>
+      </c>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F69" s="31"/>
+      <c r="G69" s="19"/>
+    </row>
+    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="18">
+        <v>68</v>
+      </c>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F70" s="31"/>
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="20">
+        <v>69</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F71" s="21"/>
+      <c r="G71" s="23"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="11">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="11">
         <v>72</v>
       </c>
-      <c r="C3" s="12">
-        <v>5130</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="12" t="s">
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="11">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="11">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="11">
         <v>80</v>
       </c>
-      <c r="F3" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <v>2</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="12">
-        <v>5130</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <v>3</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="12">
-        <v>5130</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="12" t="s">
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11">
         <v>81</v>
       </c>
-      <c r="F5" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>4</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="12">
-        <v>5130</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="12" t="s">
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="11">
         <v>82</v>
       </c>
-      <c r="F6" s="12">
-        <v>120</v>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="11">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4330971E-46F0-4063-9D60-3EA0B29B5B12}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -1238,7 +3427,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -1247,39 +3436,95 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5">
+        <v>5121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7">
+        <v>5173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1289,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9C70A4-AF5C-4FEB-AEFC-E875D37DF429}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -1302,70 +3547,70 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="25">
         <v>5130</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="25">
         <v>2025</v>
       </c>
-      <c r="E3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" t="s">
-        <v>90</v>
+      <c r="E3" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="26">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>5130</v>
@@ -1373,31 +3618,421 @@
       <c r="D4">
         <v>2024</v>
       </c>
-      <c r="E4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" t="s">
-        <v>90</v>
-      </c>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="27">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="28">
         <v>5130</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="28">
         <v>2023</v>
       </c>
-      <c r="E5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" t="s">
-        <v>90</v>
+      <c r="E5" s="28"/>
+      <c r="F5" s="23"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="24">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="25">
+        <v>5401</v>
+      </c>
+      <c r="D6" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="26">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>5401</v>
+      </c>
+      <c r="D7">
+        <v>2024</v>
+      </c>
+      <c r="F7" s="19"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <v>6</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="28">
+        <v>5401</v>
+      </c>
+      <c r="D8" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="23"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="24">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="25">
+        <v>5121</v>
+      </c>
+      <c r="D9" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="27">
+        <v>9</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="24">
+        <v>10</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="19"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
+        <v>12</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="23"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="24">
+        <v>13</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="26">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="19"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>15</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="24">
+        <v>16</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="25">
+        <v>5173</v>
+      </c>
+      <c r="D18" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E18" s="25"/>
+      <c r="F18" s="17"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="26">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19">
+        <v>2024</v>
+      </c>
+      <c r="E19" s="29">
+        <v>1.02</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="27">
+        <v>18</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E20" s="30">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="24">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="17"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="26">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22">
+        <v>2024</v>
+      </c>
+      <c r="E22" s="29">
+        <v>0.78</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="27">
+        <v>21</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E23" s="30">
+        <v>0.9</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="17"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="26">
+        <v>23</v>
+      </c>
+      <c r="D25">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="19"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="27">
+        <v>24</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E26" s="28"/>
+      <c r="F26" s="23"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="24">
+        <v>25</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E27" s="25"/>
+      <c r="F27" s="17"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="26">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>2024</v>
+      </c>
+      <c r="E28" s="29">
+        <v>0.71</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="27">
+        <v>27</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E29" s="30">
+        <v>0.65</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="24">
+        <v>28</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="34">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="26">
+        <v>29</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="33">
+        <v>2024</v>
+      </c>
+      <c r="E31" s="36">
+        <v>0.75</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="27">
+        <v>30</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="37">
+        <v>2023</v>
+      </c>
+      <c r="E32" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw_data/nashik_raw_data.xlsx
+++ b/data/raw_data/nashik_raw_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Farheen\DSE-Compass\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F010815F-5D34-47AE-8B53-CABEC2060CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD79C2F-4A89-4734-A035-CE6B67A76A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="college_details" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="296">
   <si>
     <t>college_id</t>
   </si>
@@ -81,10 +81,6 @@
   <si>
     <t>INTEGER
 (nn)</t>
-  </si>
-  <si>
-    <t>INTEGER
-(nn, uq)</t>
   </si>
   <si>
     <t>VARCHAR
@@ -325,9 +321,6 @@
     <t>regular_intake</t>
   </si>
   <si>
-    <t>latest_dse_intake</t>
-  </si>
-  <si>
     <t>Survey No 48, Gowardhan, Gangapur Road, Nashik, Maharashtra 422222, India.</t>
   </si>
   <si>
@@ -586,9 +579,6 @@
     <t>ugc_recognized</t>
   </si>
   <si>
-    <t>yes (section - 2(f), 12(B))</t>
-  </si>
-  <si>
     <t>MVP Karmaveer Adv. Baburao Ganpatrao Thakare College of Engineering</t>
   </si>
   <si>
@@ -650,13 +640,320 @@
   </si>
   <si>
     <t>3.50 L - 4.12 L</t>
+  </si>
+  <si>
+    <t>RHSCOEMSR</t>
+  </si>
+  <si>
+    <t>R.H. Sapat College of Engineering, Management Studies &amp; Research</t>
+  </si>
+  <si>
+    <t>Prin. T. A. Kulkarni Vidyanagar, College Road, Nashik - 422005</t>
+  </si>
+  <si>
+    <t>0253 2311942</t>
+  </si>
+  <si>
+    <t>https://ges-coengg.org/</t>
+  </si>
+  <si>
+    <t>1.72 L - 2.46 L</t>
+  </si>
+  <si>
+    <t>2.8 L</t>
+  </si>
+  <si>
+    <t>2.82 L</t>
+  </si>
+  <si>
+    <t>provides diploma courses, no be/btech</t>
+  </si>
+  <si>
+    <t>Sandip Institute of Engineering and Management</t>
+  </si>
+  <si>
+    <t>SIEM</t>
+  </si>
+  <si>
+    <t>Mahiravani</t>
+  </si>
+  <si>
+    <t>XM69+P4H, Trimbakeshwar Rd, Mahiravni, Nashik, Maharashtra 422213</t>
+  </si>
+  <si>
+    <t>3.86 L</t>
+  </si>
+  <si>
+    <t>https://siem.sandipfoundation.org/</t>
+  </si>
+  <si>
+    <t>4.75 L</t>
+  </si>
+  <si>
+    <t>guru gobind singh</t>
+  </si>
+  <si>
+    <t>Sandip Institute of Technology &amp; Research Centre</t>
+  </si>
+  <si>
+    <t>SITRC</t>
+  </si>
+  <si>
+    <t>XM89+87J, Trimbakeshwar Rd, Mahiravni, Nashik, Maharashtra 422213</t>
+  </si>
+  <si>
+    <t>1800 233 2714</t>
+  </si>
+  <si>
+    <t>https://sitrc.sandipfoundation.org/</t>
+  </si>
+  <si>
+    <t>Computer Science</t>
+  </si>
+  <si>
+    <t>2.86 L - 4.19 L</t>
+  </si>
+  <si>
+    <t>Sandip University</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
+    <t>1800 212 2714</t>
+  </si>
+  <si>
+    <t>Sandip University, Mahiravani, Tal &amp; Dist: Nashik - 422213, Trambakeshwar Rd, Nashik, Maharashtra 422213</t>
+  </si>
+  <si>
+    <t>INTEGER
+(n, uq)</t>
+  </si>
+  <si>
+    <t>participates_in_cap</t>
+  </si>
+  <si>
+    <t>https://www.sandipuniversity.edu.in/</t>
+  </si>
+  <si>
+    <t>4.50 L - 9.13 L</t>
+  </si>
+  <si>
+    <t>ugc_approved_section</t>
+  </si>
+  <si>
+    <t>2(f), 12(B)</t>
+  </si>
+  <si>
+    <t>2(f)</t>
+  </si>
+  <si>
+    <t>Computer Science &amp; Engineering</t>
+  </si>
+  <si>
+    <t>Cloud Technology &amp; Information Security</t>
+  </si>
+  <si>
+    <t>Cyber Security &amp; Forensics</t>
+  </si>
+  <si>
+    <t>Full Stack Development &amp; Testing (with AI &amp; ML)</t>
+  </si>
+  <si>
+    <t>Robotics Process Automation</t>
+  </si>
+  <si>
+    <t>Virtual &amp; Augmented Reality</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering</t>
+  </si>
+  <si>
+    <t>Aeronautical Engineering</t>
+  </si>
+  <si>
+    <t>Biomedical Engineering</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>CSE</t>
+  </si>
+  <si>
+    <t>CTIS</t>
+  </si>
+  <si>
+    <t>CSF</t>
+  </si>
+  <si>
+    <t>RPA</t>
+  </si>
+  <si>
+    <t>FSDT</t>
+  </si>
+  <si>
+    <t>VRAR</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>AEN</t>
+  </si>
+  <si>
+    <t>BME</t>
+  </si>
+  <si>
+    <t>BT</t>
+  </si>
+  <si>
+    <t>30-60</t>
+  </si>
+  <si>
+    <t>120-180</t>
+  </si>
+  <si>
+    <t>dse_intake_2025</t>
+  </si>
+  <si>
+    <t>70-80%</t>
+  </si>
+  <si>
+    <t>70-75%</t>
+  </si>
+  <si>
+    <t>80-85%</t>
+  </si>
+  <si>
+    <t>4.00 - 4.50 L</t>
+  </si>
+  <si>
+    <t>3.80 - 4.20 L</t>
+  </si>
+  <si>
+    <t>4.50 - 5.50 L</t>
+  </si>
+  <si>
+    <t>S.M.E.S. Sanghavi College of Engineering</t>
+  </si>
+  <si>
+    <t>0253 230 7630</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>SCOE</t>
+  </si>
+  <si>
+    <t>Varvandi / Dindori</t>
+  </si>
+  <si>
+    <t>Gut No. 166, Mhasrul-Varvandi Road, Varvandi, Taluka Dindori - 422202</t>
+  </si>
+  <si>
+    <t>https://engineering.shreemahavir.org/</t>
+  </si>
+  <si>
+    <t>2.9 L</t>
+  </si>
+  <si>
+    <t>35-40%</t>
+  </si>
+  <si>
+    <t>4.1 L</t>
+  </si>
+  <si>
+    <t>3.0 L</t>
+  </si>
+  <si>
+    <t>50-60%</t>
+  </si>
+  <si>
+    <t>Shatabdi Institute of Engineering and Research</t>
+  </si>
+  <si>
+    <t>RR8J+68C, Agaskhind, (Via Deolali Camp - Bhagur), Post-Shenit, Tal, Dist, Sinnar, Maharashtra 422502</t>
+  </si>
+  <si>
+    <t>Sinnar</t>
+  </si>
+  <si>
+    <t>02551 304 203</t>
+  </si>
+  <si>
+    <t>SIER</t>
+  </si>
+  <si>
+    <t>Electrionics &amp; Telecommunication Engineering</t>
+  </si>
+  <si>
+    <t>https://siernashik.org.in/</t>
+  </si>
+  <si>
+    <t>2.6 L</t>
+  </si>
+  <si>
+    <t>Sir Visvesvaraya Institute of Technology</t>
+  </si>
+  <si>
+    <t>SVIT</t>
+  </si>
+  <si>
+    <t>A/P Chincholi, Taluka Sinnar, Nashik - 422102</t>
+  </si>
+  <si>
+    <t>2.97 L</t>
+  </si>
+  <si>
+    <t>https://svitnashik.in/</t>
+  </si>
+  <si>
+    <t>75-80%</t>
+  </si>
+  <si>
+    <t>5.80 L</t>
+  </si>
+  <si>
+    <t>4.50 L</t>
+  </si>
+  <si>
+    <t>3.50-4.50 L</t>
+  </si>
+  <si>
+    <t>58-100%</t>
+  </si>
+  <si>
+    <t>SND College of Engineering and Research Center</t>
+  </si>
+  <si>
+    <t>SNDCOERC</t>
+  </si>
+  <si>
+    <t>Lasalgaon Patoda Yeola Rd, Yeola, Babhulgaon Bk., Maharashtra 423401, India</t>
+  </si>
+  <si>
+    <t>2559 225 011</t>
+  </si>
+  <si>
+    <t>https://sndcoe.ac.in/</t>
+  </si>
+  <si>
+    <t>Yeola</t>
+  </si>
+  <si>
+    <t>Mechatronics Engineering</t>
+  </si>
+  <si>
+    <t>1.79 L - 2.56 L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -713,6 +1010,17 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Cambria"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -822,7 +1130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -888,16 +1196,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1180,18 +1490,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.77734375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="18" width="15.77734375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="20" width="15.77734375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1205,81 +1516,87 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>20</v>
@@ -1288,22 +1605,28 @@
         <v>19</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="5" t="s">
+      <c r="S2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -1311,55 +1634,58 @@
         <v>5130</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="S3" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="R3" s="6">
+      <c r="T3" s="6">
         <v>2008</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -1367,55 +1693,58 @@
         <v>5401</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="6" t="s">
+      <c r="L4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" s="7" t="s">
+      <c r="P4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R4" s="6">
+      <c r="T4" s="6">
         <v>2012</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -1423,55 +1752,61 @@
         <v>5121</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="G5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="P5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="R5" s="6">
+      <c r="S5" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T5" s="6">
         <v>1984</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -1479,111 +1814,117 @@
         <v>5390</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="S6" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="R6" s="6">
+      <c r="T6" s="6">
         <v>2011</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="P7" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="R7" s="6">
+      <c r="S7" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="T7" s="6">
         <v>2009</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -1591,55 +1932,61 @@
         <v>5173</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>148</v>
       </c>
       <c r="G8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="J8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O8" s="6">
+        <v>2556253750</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="M8" s="6">
-        <v>2556253750</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="R8" s="6">
+      <c r="S8" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="T8" s="6">
         <v>2004</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -1647,55 +1994,61 @@
         <v>5177</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="G9" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O9" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="P9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="S9" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="R9" s="6">
+      <c r="T9" s="6">
         <v>2008</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -1703,55 +2056,58 @@
         <v>5151</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="G10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="S10" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="R10" s="6">
+      <c r="T10" s="6">
         <v>2006</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -1759,55 +2115,61 @@
         <v>5108</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O11" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="P11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="S11" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="R11" s="6">
+      <c r="T11" s="6">
         <v>1999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -1815,67 +2177,574 @@
         <v>5330</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="S12" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="T12" s="6">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>11</v>
+      </c>
+      <c r="B13" s="11">
+        <v>5181</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="6" t="s">
+      <c r="J13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="N12" s="6" t="s">
+      <c r="K13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="O13" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="P12" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="R12" s="6">
-        <v>2010</v>
-      </c>
+      <c r="R13" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="T13" s="6">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>12</v>
+      </c>
+      <c r="B14" s="11">
+        <v>5331</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="T14" s="6">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>13</v>
+      </c>
+      <c r="B15" s="11">
+        <v>5109</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="T15" s="6">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="T16" s="6">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>15</v>
+      </c>
+      <c r="B17" s="11">
+        <v>5399</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="T17" s="6">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <v>16</v>
+      </c>
+      <c r="B18" s="11">
+        <v>5184</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="T18" s="6">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>17</v>
+      </c>
+      <c r="B19" s="11">
+        <v>5125</v>
+      </c>
+      <c r="C19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="O19" s="35">
+        <v>9423787347</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="T19" s="6">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>18</v>
+      </c>
+      <c r="B20" s="11">
+        <v>5124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>288</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="T20" s="6">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O22"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O24"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O25"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O26"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q3" r:id="rId1" xr:uid="{F6E512A5-F9E2-4046-B4C3-5669B0DEE808}"/>
-    <hyperlink ref="Q5" r:id="rId2" xr:uid="{0B6C0AF0-5D3F-4832-840F-5488BCA44B6B}"/>
-    <hyperlink ref="Q4" r:id="rId3" xr:uid="{17C90922-4F15-4D49-B9ED-880F1E353D69}"/>
-    <hyperlink ref="Q6" r:id="rId4" xr:uid="{42100117-AB83-428B-A302-F1C57C11EB2E}"/>
-    <hyperlink ref="Q7" r:id="rId5" xr:uid="{149D5733-5816-468B-87D8-EB61A262AD54}"/>
-    <hyperlink ref="Q8" r:id="rId6" xr:uid="{5EF54DA0-9733-4F5D-A0FB-B54DED2F5903}"/>
-    <hyperlink ref="Q9" r:id="rId7" xr:uid="{4DC4D018-AB2C-4C55-9695-DF499D9CB60E}"/>
-    <hyperlink ref="Q10" r:id="rId8" xr:uid="{FFB3ECAC-D848-4E15-970D-68B028BECAD0}"/>
-    <hyperlink ref="Q11" r:id="rId9" xr:uid="{D947DA4C-7292-44A1-BD7F-81848DC873C7}"/>
-    <hyperlink ref="M12" r:id="rId10" display="https://www.google.com/search?q=pune+vidyarthi+griha%27s+college+of+engineering+nashik&amp;sca_esv=8712aa7b0522de6e&amp;rlz=1C1RXQR_enIN1094IN1094&amp;sxsrf=APpeQntmnHnluQT8yVmJNDjaeRoh0FECRg%3A1781875280314&amp;ei=UEI1atHcEtiUseMPiuvboAE&amp;biw=767&amp;bih=730&amp;ved=0ahUKEwjRxPfYspOVAxVYSmwGHYr1FhQQ4dUDCBI&amp;uact=5&amp;oq=pune+vidyarthi+griha%27s+college+of+engineering+nashik&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiNHB1bmUgdmlkeWFydGhpIGdyaWhhJ3MgY29sbGVnZSBvZiBlbmdpbmVlcmluZyBuYXNoaWtIAFAAWABwAHgBkAEAmAEAoAEAqgEAuAEDyAEA-AEBmAIAoAIAmAMAkgcAoAcAsgcAuAcAwgcAyAcAgAgB&amp;sclient=gws-wiz-serp" xr:uid="{781D89A6-6713-4250-95E3-16EC255163F0}"/>
-    <hyperlink ref="Q12" r:id="rId11" xr:uid="{34647692-C414-4AF3-A409-B1F9853569FD}"/>
+    <hyperlink ref="S3" r:id="rId1" xr:uid="{F6E512A5-F9E2-4046-B4C3-5669B0DEE808}"/>
+    <hyperlink ref="S5" r:id="rId2" xr:uid="{0B6C0AF0-5D3F-4832-840F-5488BCA44B6B}"/>
+    <hyperlink ref="S4" r:id="rId3" xr:uid="{17C90922-4F15-4D49-B9ED-880F1E353D69}"/>
+    <hyperlink ref="S6" r:id="rId4" xr:uid="{42100117-AB83-428B-A302-F1C57C11EB2E}"/>
+    <hyperlink ref="S7" r:id="rId5" xr:uid="{149D5733-5816-468B-87D8-EB61A262AD54}"/>
+    <hyperlink ref="S8" r:id="rId6" xr:uid="{5EF54DA0-9733-4F5D-A0FB-B54DED2F5903}"/>
+    <hyperlink ref="S9" r:id="rId7" xr:uid="{4DC4D018-AB2C-4C55-9695-DF499D9CB60E}"/>
+    <hyperlink ref="S10" r:id="rId8" xr:uid="{FFB3ECAC-D848-4E15-970D-68B028BECAD0}"/>
+    <hyperlink ref="S11" r:id="rId9" xr:uid="{D947DA4C-7292-44A1-BD7F-81848DC873C7}"/>
+    <hyperlink ref="O12" r:id="rId10" display="https://www.google.com/search?q=pune+vidyarthi+griha%27s+college+of+engineering+nashik&amp;sca_esv=8712aa7b0522de6e&amp;rlz=1C1RXQR_enIN1094IN1094&amp;sxsrf=APpeQntmnHnluQT8yVmJNDjaeRoh0FECRg%3A1781875280314&amp;ei=UEI1atHcEtiUseMPiuvboAE&amp;biw=767&amp;bih=730&amp;ved=0ahUKEwjRxPfYspOVAxVYSmwGHYr1FhQQ4dUDCBI&amp;uact=5&amp;oq=pune+vidyarthi+griha%27s+college+of+engineering+nashik&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiNHB1bmUgdmlkeWFydGhpIGdyaWhhJ3MgY29sbGVnZSBvZiBlbmdpbmVlcmluZyBuYXNoaWtIAFAAWABwAHgBkAEAmAEAoAEAqgEAuAEDyAEA-AEBmAIAoAIAmAMAkgcAoAcAsgcAuAcAwgcAyAcAgAgB&amp;sclient=gws-wiz-serp" xr:uid="{781D89A6-6713-4250-95E3-16EC255163F0}"/>
+    <hyperlink ref="S12" r:id="rId11" xr:uid="{34647692-C414-4AF3-A409-B1F9853569FD}"/>
+    <hyperlink ref="S13" r:id="rId12" xr:uid="{DF5BE269-A211-4BF5-8DE3-9F91BAD300D5}"/>
+    <hyperlink ref="S14" r:id="rId13" xr:uid="{87968F44-B5F2-42CD-A622-7DA0F0609F9E}"/>
+    <hyperlink ref="S15" r:id="rId14" xr:uid="{90D32D79-5853-4810-86D1-2E7AA9952AA1}"/>
+    <hyperlink ref="S16" r:id="rId15" xr:uid="{3D7F2EFB-6841-453E-A4E9-5A035E32A051}"/>
+    <hyperlink ref="S17" r:id="rId16" xr:uid="{B02DA78D-2067-4F8D-A85E-5855819D1624}"/>
+    <hyperlink ref="S18" r:id="rId17" xr:uid="{4FB6B601-F8B5-4583-BE90-AE762F258A41}"/>
+    <hyperlink ref="S19" r:id="rId18" xr:uid="{DBEF75DC-DC2B-430F-8F05-224AEB300210}"/>
+    <hyperlink ref="S20" r:id="rId19" xr:uid="{2B27821C-BE8C-4A18-89A2-ABC011907817}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1883,136 +2752,144 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C10441-00F6-428B-8BE2-0782171B2BC2}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="H16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2023,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFA7DCD-D4FF-479A-B6E2-9169105A0CFA}">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
@@ -2037,7 +2914,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>3</v>
@@ -2046,16 +2923,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>88</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2063,22 +2940,22 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2086,16 +2963,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="15">
         <v>5130</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" s="15">
         <v>60</v>
@@ -2107,16 +2984,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="11">
         <v>5130</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="11">
         <v>60</v>
@@ -2128,16 +3005,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="11">
         <v>5130</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="11">
         <v>60</v>
@@ -2149,16 +3026,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="21">
         <v>5130</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" s="21">
         <v>120</v>
@@ -2170,16 +3047,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" s="15">
         <v>5401</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" s="15">
         <v>120</v>
@@ -2191,16 +3068,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="11">
         <v>5401</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F8" s="11">
         <v>120</v>
@@ -2212,16 +3089,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="11">
         <v>5401</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F9" s="11">
         <v>120</v>
@@ -2233,16 +3110,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11">
         <v>5401</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" s="11">
         <v>60</v>
@@ -2254,16 +3131,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="11">
         <v>5401</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" s="11">
         <v>23</v>
@@ -2275,16 +3152,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="11">
         <v>5401</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="11">
         <v>46</v>
@@ -2296,16 +3173,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" s="11">
         <v>5401</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F13" s="11">
         <v>60</v>
@@ -2317,16 +3194,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="21">
         <v>5401</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F14" s="21">
         <v>60</v>
@@ -2338,16 +3215,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C15" s="15">
         <v>5121</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="15">
         <v>120</v>
@@ -2359,16 +3236,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C16" s="11">
         <v>5121</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F16" s="11">
         <v>120</v>
@@ -2380,16 +3257,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" s="11">
         <v>5121</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="11">
         <v>120</v>
@@ -2401,16 +3278,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C18" s="11">
         <v>5121</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="11">
         <v>120</v>
@@ -2422,16 +3299,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" s="11">
         <v>5121</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="11">
         <v>120</v>
@@ -2443,16 +3320,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>99</v>
+        <v>289</v>
       </c>
       <c r="C20" s="11">
         <v>5121</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F20" s="11">
         <v>60</v>
@@ -2464,16 +3341,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C21" s="11">
         <v>5121</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F21" s="11">
         <v>120</v>
@@ -2485,16 +3362,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C22" s="11">
         <v>5121</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F22" s="11">
         <v>120</v>
@@ -2506,16 +3383,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C23" s="11">
         <v>5121</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F23" s="11">
         <v>120</v>
@@ -2527,16 +3404,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C24" s="21">
         <v>5121</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F24" s="21">
         <v>120</v>
@@ -2548,16 +3425,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" s="15">
         <v>5390</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F25" s="15">
         <v>60</v>
@@ -2569,16 +3446,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C26" s="11">
         <v>5390</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="11">
         <v>60</v>
@@ -2590,16 +3467,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C27" s="11">
         <v>5390</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F27" s="11">
         <v>30</v>
@@ -2611,16 +3488,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C28" s="11">
         <v>5390</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" s="11">
         <v>60</v>
@@ -2632,16 +3509,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C29" s="11">
         <v>5390</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" s="11">
         <v>60</v>
@@ -2653,16 +3530,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C30" s="21">
         <v>5390</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F30" s="21">
         <v>60</v>
@@ -2674,16 +3551,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F31" s="15">
         <v>120</v>
@@ -2695,16 +3572,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F32" s="11">
         <v>120</v>
@@ -2716,16 +3593,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>142</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F33" s="11">
         <v>60</v>
@@ -2737,16 +3614,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" s="11">
         <v>60</v>
@@ -2758,16 +3635,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F35" s="11">
         <v>120</v>
@@ -2779,16 +3656,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F36" s="21">
         <v>60</v>
@@ -2800,16 +3677,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C37" s="15">
         <v>5173</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F37" s="15">
         <v>126</v>
@@ -2821,13 +3698,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F38" s="11">
         <v>63</v>
@@ -2839,10 +3716,10 @@
         <v>37</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F39" s="11">
         <v>189</v>
@@ -2854,10 +3731,10 @@
         <v>38</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F40" s="11">
         <v>63</v>
@@ -2871,10 +3748,10 @@
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F41" s="21">
         <v>63</v>
@@ -2886,14 +3763,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F42" s="15">
         <v>120</v>
@@ -2905,10 +3782,10 @@
         <v>41</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F43" s="11">
         <v>60</v>
@@ -2920,10 +3797,10 @@
         <v>42</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F44" s="11">
         <v>180</v>
@@ -2935,10 +3812,10 @@
         <v>43</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F45" s="11">
         <v>60</v>
@@ -2950,10 +3827,10 @@
         <v>44</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F46" s="11">
         <v>120</v>
@@ -2965,10 +3842,10 @@
         <v>45</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F47" s="11">
         <v>120</v>
@@ -2980,10 +3857,10 @@
         <v>46</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F48" s="11">
         <v>120</v>
@@ -2997,10 +3874,10 @@
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F49" s="21">
         <v>120</v>
@@ -3012,14 +3889,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C50" s="15"/>
       <c r="D50" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F50" s="15">
         <v>120</v>
@@ -3031,10 +3908,10 @@
         <v>49</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F51" s="11">
         <v>120</v>
@@ -3046,10 +3923,10 @@
         <v>50</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F52" s="11">
         <v>120</v>
@@ -3061,10 +3938,10 @@
         <v>51</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F53" s="11">
         <v>60</v>
@@ -3076,10 +3953,10 @@
         <v>52</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F54" s="11">
         <v>120</v>
@@ -3091,10 +3968,10 @@
         <v>53</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F55" s="11">
         <v>60</v>
@@ -3106,10 +3983,10 @@
         <v>54</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F56" s="11">
         <v>60</v>
@@ -3123,10 +4000,10 @@
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F57" s="21">
         <v>60</v>
@@ -3138,11 +4015,11 @@
         <v>56</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="15">
@@ -3155,7 +4032,7 @@
         <v>57</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F59" s="11">
         <v>180</v>
@@ -3167,7 +4044,7 @@
         <v>58</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F60" s="11">
         <v>60</v>
@@ -3179,7 +4056,7 @@
         <v>59</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F61" s="11">
         <v>120</v>
@@ -3191,7 +4068,7 @@
         <v>60</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F62" s="11">
         <v>120</v>
@@ -3203,7 +4080,7 @@
         <v>61</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F63" s="11">
         <v>180</v>
@@ -3215,7 +4092,7 @@
         <v>62</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F64" s="11">
         <v>180</v>
@@ -3227,7 +4104,7 @@
         <v>63</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F65" s="11">
         <v>60</v>
@@ -3241,7 +4118,7 @@
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21">
@@ -3254,14 +4131,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C67" s="15"/>
       <c r="D67" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F67" s="15"/>
       <c r="G67" s="17"/>
@@ -3270,45 +4147,36 @@
       <c r="A68" s="18">
         <v>66</v>
       </c>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="E68" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="F68" s="31"/>
+      <c r="D68" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="G68" s="19"/>
     </row>
     <row r="69" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="18">
         <v>67</v>
       </c>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="E69" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="F69" s="31"/>
+      <c r="D69" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="G69" s="19"/>
     </row>
     <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="18">
         <v>68</v>
       </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E70" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="F70" s="31"/>
+      <c r="D70" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="G70" s="19"/>
     </row>
     <row r="71" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -3318,92 +4186,961 @@
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F71" s="21"/>
       <c r="G71" s="23"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="11">
+    <row r="72" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="14">
         <v>70</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="11">
+      <c r="B72" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C72" s="15"/>
+      <c r="D72" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15">
+        <v>60</v>
+      </c>
+      <c r="G72" s="17"/>
+    </row>
+    <row r="73" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="18">
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="11">
+      <c r="D73" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="11">
+        <v>60</v>
+      </c>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="18">
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="11">
+      <c r="D74" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F74" s="11">
+        <v>120</v>
+      </c>
+      <c r="G74" s="19"/>
+    </row>
+    <row r="75" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="18">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="11">
+      <c r="D75" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F75" s="11">
+        <v>120</v>
+      </c>
+      <c r="G75" s="19"/>
+    </row>
+    <row r="76" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="18">
         <v>74</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="11">
+      <c r="D76" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F76" s="11">
+        <v>120</v>
+      </c>
+      <c r="G76" s="19"/>
+    </row>
+    <row r="77" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="20">
         <v>75</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="11">
+      <c r="B77" s="21"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21">
+        <v>120</v>
+      </c>
+      <c r="G77" s="23"/>
+    </row>
+    <row r="78" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="14">
         <v>76</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="11">
+      <c r="B78" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C78" s="15"/>
+      <c r="D78" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15">
+        <v>60</v>
+      </c>
+      <c r="G78" s="17"/>
+    </row>
+    <row r="79" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="18">
         <v>77</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="11">
+      <c r="D79" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F79" s="11">
+        <v>180</v>
+      </c>
+      <c r="G79" s="19"/>
+    </row>
+    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="18">
         <v>78</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="11">
+      <c r="D80" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F80" s="11">
+        <v>60</v>
+      </c>
+      <c r="G80" s="19"/>
+    </row>
+    <row r="81" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="18">
         <v>79</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="11">
+      <c r="D81" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F81" s="11">
+        <v>120</v>
+      </c>
+      <c r="G81" s="19"/>
+    </row>
+    <row r="82" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="18">
         <v>80</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="11">
+      <c r="D82" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F82" s="11">
+        <v>120</v>
+      </c>
+      <c r="G82" s="19"/>
+    </row>
+    <row r="83" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="18">
         <v>81</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="11">
+      <c r="D83" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F83" s="11">
+        <v>60</v>
+      </c>
+      <c r="G83" s="19"/>
+    </row>
+    <row r="84" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="18">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="11">
+      <c r="D84" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F84" s="11">
+        <v>60</v>
+      </c>
+      <c r="G84" s="19"/>
+    </row>
+    <row r="85" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="20">
         <v>83</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="11">
+      <c r="B85" s="21"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21">
+        <v>60</v>
+      </c>
+      <c r="G85" s="23"/>
+    </row>
+    <row r="86" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="14">
         <v>84</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="11">
+      <c r="B86" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" s="15"/>
+      <c r="D86" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E86" s="15"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="17"/>
+    </row>
+    <row r="87" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="18">
         <v>85</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G87" s="19"/>
+    </row>
+    <row r="88" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="18">
+        <v>86</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G88" s="19"/>
+    </row>
+    <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="18">
+        <v>87</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G89" s="19"/>
+    </row>
+    <row r="90" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="18">
+        <v>88</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G90" s="19"/>
+    </row>
+    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="18">
+        <v>89</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G91" s="19"/>
+    </row>
+    <row r="92" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A92" s="18">
+        <v>90</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G92" s="19"/>
+    </row>
+    <row r="93" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="18">
+        <v>91</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G93" s="19"/>
+    </row>
+    <row r="94" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="18">
+        <v>92</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G94" s="19"/>
+    </row>
+    <row r="95" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="20">
+        <v>93</v>
+      </c>
+      <c r="B95" s="21"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E95" s="21"/>
+      <c r="F95" s="21"/>
+      <c r="G95" s="23"/>
+    </row>
+    <row r="96" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A96" s="14">
+        <v>94</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C96" s="15"/>
+      <c r="D96" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G96" s="17"/>
+    </row>
+    <row r="97" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="18">
+        <v>95</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F97" s="11">
+        <v>60</v>
+      </c>
+      <c r="G97" s="19"/>
+    </row>
+    <row r="98" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A98" s="18">
+        <v>96</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F98" s="11">
+        <v>60</v>
+      </c>
+      <c r="G98" s="19"/>
+    </row>
+    <row r="99" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="18">
+        <v>97</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E99" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F99" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G99" s="19"/>
+    </row>
+    <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A100" s="18">
+        <v>98</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G100" s="19"/>
+    </row>
+    <row r="101" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="18">
+        <v>99</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G101" s="19"/>
+    </row>
+    <row r="102" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A102" s="18">
+        <v>100</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F102" s="11">
+        <v>30</v>
+      </c>
+      <c r="G102" s="19"/>
+    </row>
+    <row r="103" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A103" s="18">
+        <v>101</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F103" s="11">
+        <v>30</v>
+      </c>
+      <c r="G103" s="19"/>
+    </row>
+    <row r="104" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="18">
+        <v>102</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G104" s="19"/>
+    </row>
+    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="18">
+        <v>103</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G105" s="19"/>
+    </row>
+    <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="18">
+        <v>104</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E106" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F106" s="11">
+        <v>60</v>
+      </c>
+      <c r="G106" s="19"/>
+    </row>
+    <row r="107" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="18">
+        <v>105</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F107" s="11">
+        <v>60</v>
+      </c>
+      <c r="G107" s="19"/>
+    </row>
+    <row r="108" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A108" s="18">
+        <v>106</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E108" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G108" s="19"/>
+    </row>
+    <row r="109" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="18">
+        <v>107</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E109" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G109" s="19"/>
+    </row>
+    <row r="110" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="18">
+        <v>108</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F110" s="11">
+        <v>30</v>
+      </c>
+      <c r="G110" s="19"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="20">
+        <v>109</v>
+      </c>
+      <c r="B111" s="21"/>
+      <c r="C111" s="21"/>
+      <c r="D111" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="E111" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="F111" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="G111" s="23"/>
+    </row>
+    <row r="112" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="14">
+        <v>110</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C112" s="15"/>
+      <c r="D112" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F112" s="15"/>
+      <c r="G112" s="17"/>
+    </row>
+    <row r="113" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A113" s="18">
+        <v>111</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G113" s="19"/>
+    </row>
+    <row r="114" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="18">
+        <v>112</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G114" s="19"/>
+    </row>
+    <row r="115" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A115" s="18">
+        <v>113</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G115" s="19"/>
+    </row>
+    <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A116" s="18">
+        <v>114</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G116" s="19"/>
+    </row>
+    <row r="117" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="20">
+        <v>115</v>
+      </c>
+      <c r="B117" s="21"/>
+      <c r="C117" s="21"/>
+      <c r="D117" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E117" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F117" s="21"/>
+      <c r="G117" s="23"/>
+    </row>
+    <row r="118" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="14">
+        <v>116</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="C118" s="15"/>
+      <c r="D118" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F118" s="15">
+        <v>60</v>
+      </c>
+      <c r="G118" s="17"/>
+    </row>
+    <row r="119" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="18">
+        <v>117</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F119" s="11">
+        <v>60</v>
+      </c>
+      <c r="G119" s="19"/>
+    </row>
+    <row r="120" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="18">
+        <v>118</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F120" s="11">
+        <v>60</v>
+      </c>
+      <c r="G120" s="19"/>
+    </row>
+    <row r="121" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="18">
+        <v>119</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F121" s="11">
+        <v>60</v>
+      </c>
+      <c r="G121" s="19"/>
+    </row>
+    <row r="122" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="20">
+        <v>120</v>
+      </c>
+      <c r="B122" s="21"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E122" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F122" s="21">
+        <v>60</v>
+      </c>
+      <c r="G122" s="23"/>
+    </row>
+    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A123" s="14">
+        <v>121</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C123" s="15"/>
+      <c r="D123" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E123" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F123" s="15">
+        <v>60</v>
+      </c>
+      <c r="G123" s="17"/>
+    </row>
+    <row r="124" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A124" s="18">
+        <v>122</v>
+      </c>
+      <c r="B124" s="33"/>
+      <c r="C124" s="33"/>
+      <c r="D124" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="E124" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F124" s="33">
+        <v>60</v>
+      </c>
+      <c r="G124" s="19"/>
+    </row>
+    <row r="125" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A125" s="18">
+        <v>123</v>
+      </c>
+      <c r="B125" s="33"/>
+      <c r="C125" s="33"/>
+      <c r="D125" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E125" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F125" s="33">
+        <v>60</v>
+      </c>
+      <c r="G125" s="19"/>
+    </row>
+    <row r="126" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="20">
+        <v>124</v>
+      </c>
+      <c r="B126" s="21"/>
+      <c r="C126" s="21"/>
+      <c r="D126" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E126" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F126" s="21">
+        <v>60</v>
+      </c>
+      <c r="G126" s="23"/>
+    </row>
+    <row r="127" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="11">
+        <v>125</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F127" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="11">
+        <v>126</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F128" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="11">
+        <v>127</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E129" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F129" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A130" s="11">
+        <v>128</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F130" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A131" s="11">
+        <v>129</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F131" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="11">
+        <v>130</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F132" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="11">
+        <v>131</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F133" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="11">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="11">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="11">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="11">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="11">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="11">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="11">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="11">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="11">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="11">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="11">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="11">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="11">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="11">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="11">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="11">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3414,7 +5151,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4330971E-46F0-4063-9D60-3EA0B29B5B12}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -3427,7 +5164,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -3436,16 +5173,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -3453,37 +5190,37 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>5121</v>
@@ -3491,12 +5228,12 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C7">
         <v>5173</v>
@@ -3504,27 +5241,67 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3534,7 +5311,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9C70A4-AF5C-4FEB-AEFC-E875D37DF429}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3547,22 +5324,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
@@ -3570,7 +5347,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -3579,10 +5356,10 @@
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -3590,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="25">
         <v>5130</v>
@@ -3599,10 +5376,10 @@
         <v>2025</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -3610,7 +5387,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>5130</v>
@@ -3625,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="28">
         <v>5130</v>
@@ -3641,7 +5418,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="25">
         <v>5401</v>
@@ -3650,10 +5427,10 @@
         <v>2025</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -3661,7 +5438,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>5401</v>
@@ -3676,7 +5453,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="28">
         <v>5401</v>
@@ -3692,7 +5469,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" s="25">
         <v>5121</v>
@@ -3701,10 +5478,10 @@
         <v>2025</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3712,7 +5489,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F10" s="19"/>
     </row>
@@ -3721,7 +5498,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
@@ -3733,17 +5510,17 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25">
         <v>2025</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3751,7 +5528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F13" s="19"/>
     </row>
@@ -3760,7 +5537,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
@@ -3772,17 +5549,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25">
         <v>2025</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3790,7 +5567,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F16" s="19"/>
     </row>
@@ -3799,7 +5576,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
@@ -3811,7 +5588,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C18" s="25">
         <v>5173</v>
@@ -3827,7 +5604,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D19">
         <v>2024</v>
@@ -3836,7 +5613,7 @@
         <v>1.02</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -3844,7 +5621,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C20" s="28"/>
       <c r="D20" s="28">
@@ -3854,7 +5631,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,7 +5639,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25">
@@ -3876,7 +5653,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D22">
         <v>2024</v>
@@ -3885,7 +5662,7 @@
         <v>0.78</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -3893,7 +5670,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28">
@@ -3903,7 +5680,7 @@
         <v>0.9</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3911,7 +5688,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25">
@@ -3946,7 +5723,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C27" s="25"/>
       <c r="D27" s="25">
@@ -3966,7 +5743,7 @@
         <v>0.71</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,7 +5759,7 @@
         <v>0.65</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3990,33 +5767,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="34">
-        <v>2025</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>193</v>
-      </c>
       <c r="F30" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="26">
         <v>29</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="33">
+      <c r="D31">
         <v>2024</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="29">
         <v>0.75</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -4025,14 +5800,425 @@
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
-      <c r="D32" s="37">
+      <c r="D32" s="28">
         <v>2023</v>
       </c>
       <c r="E32" s="30">
         <v>0.8</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="24">
+        <v>31</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E33" s="25"/>
+      <c r="F33" s="17"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="26">
+        <v>32</v>
+      </c>
+      <c r="D34">
+        <v>2024</v>
+      </c>
+      <c r="E34" s="29">
+        <v>1.51</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="27">
+        <v>33</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E35" s="30">
+        <v>1.57</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="24">
+        <v>34</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E36" s="25"/>
+      <c r="F36" s="17"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="26">
+        <v>35</v>
+      </c>
+      <c r="D37">
+        <v>2024</v>
+      </c>
+      <c r="E37" s="29">
+        <v>1.78</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="27">
+        <v>36</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E38" s="30">
+        <v>0.74</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="24">
+        <v>37</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E39" s="25"/>
+      <c r="F39" s="17"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="26">
+        <v>38</v>
+      </c>
+      <c r="D40">
+        <v>2024</v>
+      </c>
+      <c r="E40" s="29">
+        <v>1</v>
+      </c>
+      <c r="F40" s="19">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <v>39</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E41" s="30">
+        <v>0.84</v>
+      </c>
+      <c r="F41" s="31">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="24">
+        <v>40</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="26">
+        <v>41</v>
+      </c>
+      <c r="D43">
+        <v>2024</v>
+      </c>
+      <c r="E43" t="s">
+        <v>253</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="27">
+        <v>42</v>
+      </c>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="24">
+        <v>43</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="26">
+        <v>44</v>
+      </c>
+      <c r="D46">
+        <v>2024</v>
+      </c>
+      <c r="E46" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <v>45</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="24">
+        <v>46</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25">
+        <v>2025</v>
+      </c>
+      <c r="E48" s="25"/>
+      <c r="F48" s="17"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="26">
+        <v>47</v>
+      </c>
+      <c r="D49">
+        <v>2024</v>
+      </c>
+      <c r="F49" s="19"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="27">
+        <v>48</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E50" s="28"/>
+      <c r="F50" s="23"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="24">
+        <v>49</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="37">
+        <v>2025</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="26">
+        <v>50</v>
+      </c>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="36">
+        <v>2024</v>
+      </c>
+      <c r="E52" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="27">
+        <v>51</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="39">
+        <v>2023</v>
+      </c>
+      <c r="E53" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="26">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="26">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="26">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="26">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="26">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="26">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="26">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="26">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="26">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="26">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="26">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="26">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="26">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="26">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="26">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="26">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="26">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
